--- a/01_AI_Governance_Risk_Compliance/1.1_RCM_Update/GT_AI_Security_and_Agent_Audit_Checklist_v2.0.xlsx
+++ b/01_AI_Governance_Risk_Compliance/1.1_RCM_Update/GT_AI_Security_and_Agent_Audit_Checklist_v2.0.xlsx
@@ -850,31 +850,31 @@
       </c>
       <c r="B15" s="8">
         <f>COUNTA(Checklist!A5:A21)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="C15" s="8">
         <f>COUNTIF(Checklist!E5:E21,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D15" s="8">
         <f>COUNTIF(Checklist!E5:E21,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
         <f>COUNTIF(Checklist!E5:E21,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F15" s="8">
         <f>B15-C15-D15-E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="9">
+        <v>17</v>
+      </c>
+      <c r="G15" s="9" t="str">
         <f>IF(C15+D15=0,"-",C15/(C15+D15))</f>
-        <v/>
-      </c>
-      <c r="H15" s="10">
+        <v>-</v>
+      </c>
+      <c r="H15" s="10" t="str">
         <f>IF(G15="-","-",IF(G15&gt;=0.9,"Low Risk",IF(G15&gt;=0.75,"Moderate Risk",IF(G15&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="16">
@@ -885,31 +885,31 @@
       </c>
       <c r="B16" s="8">
         <f>COUNTA(Checklist!A23:A37)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C16" s="8">
         <f>COUNTIF(Checklist!E23:E37,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D16" s="8">
         <f>COUNTIF(Checklist!E23:E37,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E16" s="8">
         <f>COUNTIF(Checklist!E23:E37,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F16" s="8">
         <f>B16-C16-D16-E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="9">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9" t="str">
         <f>IF(C16+D16=0,"-",C16/(C16+D16))</f>
-        <v/>
-      </c>
-      <c r="H16" s="10">
+        <v>-</v>
+      </c>
+      <c r="H16" s="10" t="str">
         <f>IF(G16="-","-",IF(G16&gt;=0.9,"Low Risk",IF(G16&gt;=0.75,"Moderate Risk",IF(G16&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="17">
@@ -920,31 +920,31 @@
       </c>
       <c r="B17" s="8">
         <f>COUNTA(Checklist!A39:A56)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="C17" s="8">
         <f>COUNTIF(Checklist!E39:E56,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D17" s="8">
         <f>COUNTIF(Checklist!E39:E56,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E17" s="8">
         <f>COUNTIF(Checklist!E39:E56,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F17" s="8">
         <f>B17-C17-D17-E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="9">
+        <v>18</v>
+      </c>
+      <c r="G17" s="9" t="str">
         <f>IF(C17+D17=0,"-",C17/(C17+D17))</f>
-        <v/>
-      </c>
-      <c r="H17" s="10">
+        <v>-</v>
+      </c>
+      <c r="H17" s="10" t="str">
         <f>IF(G17="-","-",IF(G17&gt;=0.9,"Low Risk",IF(G17&gt;=0.75,"Moderate Risk",IF(G17&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="18">
@@ -955,31 +955,31 @@
       </c>
       <c r="B18" s="8">
         <f>COUNTA(Checklist!A58:A65)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C18" s="8">
         <f>COUNTIF(Checklist!E58:E65,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D18" s="8">
         <f>COUNTIF(Checklist!E58:E65,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E18" s="8">
         <f>COUNTIF(Checklist!E58:E65,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F18" s="8">
         <f>B18-C18-D18-E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="9">
+        <v>8</v>
+      </c>
+      <c r="G18" s="9" t="str">
         <f>IF(C18+D18=0,"-",C18/(C18+D18))</f>
-        <v/>
-      </c>
-      <c r="H18" s="10">
+        <v>-</v>
+      </c>
+      <c r="H18" s="10" t="str">
         <f>IF(G18="-","-",IF(G18&gt;=0.9,"Low Risk",IF(G18&gt;=0.75,"Moderate Risk",IF(G18&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="19">
@@ -990,31 +990,31 @@
       </c>
       <c r="B19" s="8">
         <f>COUNTA(Checklist!A67:A81)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C19" s="8">
         <f>COUNTIF(Checklist!E67:E81,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D19" s="8">
         <f>COUNTIF(Checklist!E67:E81,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E19" s="8">
         <f>COUNTIF(Checklist!E67:E81,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F19" s="8">
         <f>B19-C19-D19-E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="9">
+        <v>15</v>
+      </c>
+      <c r="G19" s="9" t="str">
         <f>IF(C19+D19=0,"-",C19/(C19+D19))</f>
-        <v/>
-      </c>
-      <c r="H19" s="10">
+        <v>-</v>
+      </c>
+      <c r="H19" s="10" t="str">
         <f>IF(G19="-","-",IF(G19&gt;=0.9,"Low Risk",IF(G19&gt;=0.75,"Moderate Risk",IF(G19&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="20">
@@ -1025,31 +1025,31 @@
       </c>
       <c r="B20" s="8">
         <f>COUNTA(Checklist!A83:A88)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C20" s="8">
         <f>COUNTIF(Checklist!E83:E88,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D20" s="8">
         <f>COUNTIF(Checklist!E83:E88,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E20" s="8">
         <f>COUNTIF(Checklist!E83:E88,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F20" s="8">
         <f>B20-C20-D20-E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="9">
+        <v>6</v>
+      </c>
+      <c r="G20" s="9" t="str">
         <f>IF(C20+D20=0,"-",C20/(C20+D20))</f>
-        <v/>
-      </c>
-      <c r="H20" s="10">
+        <v>-</v>
+      </c>
+      <c r="H20" s="10" t="str">
         <f>IF(G20="-","-",IF(G20&gt;=0.9,"Low Risk",IF(G20&gt;=0.75,"Moderate Risk",IF(G20&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="21">
@@ -1060,31 +1060,31 @@
       </c>
       <c r="B21" s="8">
         <f>COUNTA(Checklist!A90:A95)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C21" s="8">
         <f>COUNTIF(Checklist!E90:E95,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D21" s="8">
         <f>COUNTIF(Checklist!E90:E95,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E21" s="8">
         <f>COUNTIF(Checklist!E90:E95,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F21" s="8">
         <f>B21-C21-D21-E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="9">
+        <v>6</v>
+      </c>
+      <c r="G21" s="9" t="str">
         <f>IF(C21+D21=0,"-",C21/(C21+D21))</f>
-        <v/>
-      </c>
-      <c r="H21" s="10">
+        <v>-</v>
+      </c>
+      <c r="H21" s="10" t="str">
         <f>IF(G21="-","-",IF(G21&gt;=0.9,"Low Risk",IF(G21&gt;=0.75,"Moderate Risk",IF(G21&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="22">
@@ -1095,31 +1095,31 @@
       </c>
       <c r="B22" s="8">
         <f>COUNTA(Checklist!A97:A119)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="C22" s="8">
         <f>COUNTIF(Checklist!E97:E119,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D22" s="8">
         <f>COUNTIF(Checklist!E97:E119,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E22" s="8">
         <f>COUNTIF(Checklist!E97:E119,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F22" s="8">
         <f>B22-C22-D22-E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="9">
+        <v>23</v>
+      </c>
+      <c r="G22" s="9" t="str">
         <f>IF(C22+D22=0,"-",C22/(C22+D22))</f>
-        <v/>
-      </c>
-      <c r="H22" s="10">
+        <v>-</v>
+      </c>
+      <c r="H22" s="10" t="str">
         <f>IF(G22="-","-",IF(G22&gt;=0.9,"Low Risk",IF(G22&gt;=0.75,"Moderate Risk",IF(G22&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="23">
@@ -1130,31 +1130,31 @@
       </c>
       <c r="B23" s="8">
         <f>COUNTA(Checklist!A121:A137)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="C23" s="8">
         <f>COUNTIF(Checklist!E121:E137,"Pass")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D23" s="8">
         <f>COUNTIF(Checklist!E121:E137,"Fail")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E23" s="8">
         <f>COUNTIF(Checklist!E121:E137,"N/A")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F23" s="8">
         <f>B23-C23-D23-E23</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
+        <v>17</v>
+      </c>
+      <c r="G23" s="9" t="str">
         <f>IF(C23+D23=0,"-",C23/(C23+D23))</f>
-        <v/>
-      </c>
-      <c r="H23" s="10">
+        <v>-</v>
+      </c>
+      <c r="H23" s="10" t="str">
         <f>IF(G23="-","-",IF(G23&gt;=0.9,"Low Risk",IF(G23&gt;=0.75,"Moderate Risk",IF(G23&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="24">
@@ -1165,31 +1165,31 @@
       </c>
       <c r="B24" s="11">
         <f>SUM(B15:B23)</f>
-        <v/>
+        <v>125</v>
       </c>
       <c r="C24" s="11">
         <f>SUM(C15:C23)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D24" s="11">
         <f>SUM(D15:D23)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E24" s="11">
         <f>SUM(E15:E23)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F24" s="11">
         <f>SUM(F15:F23)</f>
-        <v/>
-      </c>
-      <c r="G24" s="12">
+        <v>125</v>
+      </c>
+      <c r="G24" s="12" t="str">
         <f>IF(C24+D24=0,"-",C24/(C24+D24))</f>
-        <v/>
-      </c>
-      <c r="H24" s="11">
+        <v>-</v>
+      </c>
+      <c r="H24" s="11" t="str">
         <f>IF(G24="-","-",IF(G24&gt;=0.9,"Low Risk",IF(G24&gt;=0.75,"Moderate Risk",IF(G24&gt;=0.6,"High Risk","Critical Risk"))))</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="25">
@@ -1200,9 +1200,9 @@
       </c>
       <c r="B25" s="10">
         <f>COUNTIFS(Checklist!E5:E137,"Fail",Checklist!F5:F137,"Critical")</f>
-        <v/>
-      </c>
-      <c r="C25" s="13">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13" t="str">
         <f>IF(B25&gt;0,"Any failed Critical item escalates the overall rating to Critical Risk regardless of score.","")</f>
         <v/>
       </c>
@@ -1213,9 +1213,9 @@
           <t>FINAL RATING</t>
         </is>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="15" t="str">
         <f>IF(B25&gt;0,"Critical Risk",H24)</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="28">
@@ -1481,7 +1481,7 @@
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
-      <c r="K5">
+      <c r="K5" t="str">
         <f>IF(E5="Fail",COUNTIF($E$5:E5,"Fail"),"")</f>
         <v/>
       </c>
@@ -1516,7 +1516,7 @@
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
-      <c r="K6">
+      <c r="K6" t="str">
         <f>IF(E6="Fail",COUNTIF($E$5:E6,"Fail"),"")</f>
         <v/>
       </c>
@@ -1551,7 +1551,7 @@
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
-      <c r="K7">
+      <c r="K7" t="str">
         <f>IF(E7="Fail",COUNTIF($E$5:E7,"Fail"),"")</f>
         <v/>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
-      <c r="K8">
+      <c r="K8" t="str">
         <f>IF(E8="Fail",COUNTIF($E$5:E8,"Fail"),"")</f>
         <v/>
       </c>
@@ -1621,7 +1621,7 @@
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
-      <c r="K9">
+      <c r="K9" t="str">
         <f>IF(E9="Fail",COUNTIF($E$5:E9,"Fail"),"")</f>
         <v/>
       </c>
@@ -1656,7 +1656,7 @@
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
-      <c r="K10">
+      <c r="K10" t="str">
         <f>IF(E10="Fail",COUNTIF($E$5:E10,"Fail"),"")</f>
         <v/>
       </c>
@@ -1691,7 +1691,7 @@
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
-      <c r="K11">
+      <c r="K11" t="str">
         <f>IF(E11="Fail",COUNTIF($E$5:E11,"Fail"),"")</f>
         <v/>
       </c>
@@ -1726,7 +1726,7 @@
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
-      <c r="K12">
+      <c r="K12" t="str">
         <f>IF(E12="Fail",COUNTIF($E$5:E12,"Fail"),"")</f>
         <v/>
       </c>
@@ -1761,7 +1761,7 @@
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
-      <c r="K13">
+      <c r="K13" t="str">
         <f>IF(E13="Fail",COUNTIF($E$5:E13,"Fail"),"")</f>
         <v/>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
-      <c r="K14">
+      <c r="K14" t="str">
         <f>IF(E14="Fail",COUNTIF($E$5:E14,"Fail"),"")</f>
         <v/>
       </c>
@@ -1831,7 +1831,7 @@
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
-      <c r="K15">
+      <c r="K15" t="str">
         <f>IF(E15="Fail",COUNTIF($E$5:E15,"Fail"),"")</f>
         <v/>
       </c>
@@ -1866,7 +1866,7 @@
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
-      <c r="K16">
+      <c r="K16" t="str">
         <f>IF(E16="Fail",COUNTIF($E$5:E16,"Fail"),"")</f>
         <v/>
       </c>
@@ -1901,7 +1901,7 @@
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
-      <c r="K17">
+      <c r="K17" t="str">
         <f>IF(E17="Fail",COUNTIF($E$5:E17,"Fail"),"")</f>
         <v/>
       </c>
@@ -1936,7 +1936,7 @@
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
-      <c r="K18">
+      <c r="K18" t="str">
         <f>IF(E18="Fail",COUNTIF($E$5:E18,"Fail"),"")</f>
         <v/>
       </c>
@@ -1971,7 +1971,7 @@
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
-      <c r="K19">
+      <c r="K19" t="str">
         <f>IF(E19="Fail",COUNTIF($E$5:E19,"Fail"),"")</f>
         <v/>
       </c>
@@ -2006,7 +2006,7 @@
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
-      <c r="K20">
+      <c r="K20" t="str">
         <f>IF(E20="Fail",COUNTIF($E$5:E20,"Fail"),"")</f>
         <v/>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
-      <c r="K21">
+      <c r="K21" t="str">
         <f>IF(E21="Fail",COUNTIF($E$5:E21,"Fail"),"")</f>
         <v/>
       </c>
@@ -2057,7 +2057,7 @@
           <t>4. Data Security</t>
         </is>
       </c>
-      <c r="K22">
+      <c r="K22" t="str">
         <f>IF(E22="Fail",COUNTIF($E$5:E22,"Fail"),"")</f>
         <v/>
       </c>
@@ -2087,7 +2087,7 @@
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
-      <c r="K23">
+      <c r="K23" t="str">
         <f>IF(E23="Fail",COUNTIF($E$5:E23,"Fail"),"")</f>
         <v/>
       </c>
@@ -2122,7 +2122,7 @@
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
-      <c r="K24">
+      <c r="K24" t="str">
         <f>IF(E24="Fail",COUNTIF($E$5:E24,"Fail"),"")</f>
         <v/>
       </c>
@@ -2157,7 +2157,7 @@
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
-      <c r="K25">
+      <c r="K25" t="str">
         <f>IF(E25="Fail",COUNTIF($E$5:E25,"Fail"),"")</f>
         <v/>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="4" t="n"/>
-      <c r="K26">
+      <c r="K26" t="str">
         <f>IF(E26="Fail",COUNTIF($E$5:E26,"Fail"),"")</f>
         <v/>
       </c>
@@ -2227,7 +2227,7 @@
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="4" t="n"/>
-      <c r="K27">
+      <c r="K27" t="str">
         <f>IF(E27="Fail",COUNTIF($E$5:E27,"Fail"),"")</f>
         <v/>
       </c>
@@ -2262,7 +2262,7 @@
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
-      <c r="K28">
+      <c r="K28" t="str">
         <f>IF(E28="Fail",COUNTIF($E$5:E28,"Fail"),"")</f>
         <v/>
       </c>
@@ -2297,7 +2297,7 @@
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
-      <c r="K29">
+      <c r="K29" t="str">
         <f>IF(E29="Fail",COUNTIF($E$5:E29,"Fail"),"")</f>
         <v/>
       </c>
@@ -2332,7 +2332,7 @@
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
-      <c r="K30">
+      <c r="K30" t="str">
         <f>IF(E30="Fail",COUNTIF($E$5:E30,"Fail"),"")</f>
         <v/>
       </c>
@@ -2367,7 +2367,7 @@
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
-      <c r="K31">
+      <c r="K31" t="str">
         <f>IF(E31="Fail",COUNTIF($E$5:E31,"Fail"),"")</f>
         <v/>
       </c>
@@ -2402,7 +2402,7 @@
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
-      <c r="K32">
+      <c r="K32" t="str">
         <f>IF(E32="Fail",COUNTIF($E$5:E32,"Fail"),"")</f>
         <v/>
       </c>
@@ -2437,7 +2437,7 @@
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
-      <c r="K33">
+      <c r="K33" t="str">
         <f>IF(E33="Fail",COUNTIF($E$5:E33,"Fail"),"")</f>
         <v/>
       </c>
@@ -2472,7 +2472,7 @@
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
-      <c r="K34">
+      <c r="K34" t="str">
         <f>IF(E34="Fail",COUNTIF($E$5:E34,"Fail"),"")</f>
         <v/>
       </c>
@@ -2507,7 +2507,7 @@
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
-      <c r="K35">
+      <c r="K35" t="str">
         <f>IF(E35="Fail",COUNTIF($E$5:E35,"Fail"),"")</f>
         <v/>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
-      <c r="K36">
+      <c r="K36" t="str">
         <f>IF(E36="Fail",COUNTIF($E$5:E36,"Fail"),"")</f>
         <v/>
       </c>
@@ -2577,7 +2577,7 @@
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
-      <c r="K37">
+      <c r="K37" t="str">
         <f>IF(E37="Fail",COUNTIF($E$5:E37,"Fail"),"")</f>
         <v/>
       </c>
@@ -2593,7 +2593,7 @@
           <t>5. Model Security</t>
         </is>
       </c>
-      <c r="K38">
+      <c r="K38" t="str">
         <f>IF(E38="Fail",COUNTIF($E$5:E38,"Fail"),"")</f>
         <v/>
       </c>
@@ -2623,7 +2623,7 @@
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="4" t="n"/>
-      <c r="K39">
+      <c r="K39" t="str">
         <f>IF(E39="Fail",COUNTIF($E$5:E39,"Fail"),"")</f>
         <v/>
       </c>
@@ -2658,7 +2658,7 @@
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
-      <c r="K40">
+      <c r="K40" t="str">
         <f>IF(E40="Fail",COUNTIF($E$5:E40,"Fail"),"")</f>
         <v/>
       </c>
@@ -2693,7 +2693,7 @@
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
-      <c r="K41">
+      <c r="K41" t="str">
         <f>IF(E41="Fail",COUNTIF($E$5:E41,"Fail"),"")</f>
         <v/>
       </c>
@@ -2728,7 +2728,7 @@
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="4" t="n"/>
-      <c r="K42">
+      <c r="K42" t="str">
         <f>IF(E42="Fail",COUNTIF($E$5:E42,"Fail"),"")</f>
         <v/>
       </c>
@@ -2763,7 +2763,7 @@
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
-      <c r="K43">
+      <c r="K43" t="str">
         <f>IF(E43="Fail",COUNTIF($E$5:E43,"Fail"),"")</f>
         <v/>
       </c>
@@ -2798,7 +2798,7 @@
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="n"/>
-      <c r="K44">
+      <c r="K44" t="str">
         <f>IF(E44="Fail",COUNTIF($E$5:E44,"Fail"),"")</f>
         <v/>
       </c>
@@ -2833,7 +2833,7 @@
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
-      <c r="K45">
+      <c r="K45" t="str">
         <f>IF(E45="Fail",COUNTIF($E$5:E45,"Fail"),"")</f>
         <v/>
       </c>
@@ -2868,7 +2868,7 @@
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
-      <c r="K46">
+      <c r="K46" t="str">
         <f>IF(E46="Fail",COUNTIF($E$5:E46,"Fail"),"")</f>
         <v/>
       </c>
@@ -2903,7 +2903,7 @@
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
-      <c r="K47">
+      <c r="K47" t="str">
         <f>IF(E47="Fail",COUNTIF($E$5:E47,"Fail"),"")</f>
         <v/>
       </c>
@@ -2938,7 +2938,7 @@
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
-      <c r="K48">
+      <c r="K48" t="str">
         <f>IF(E48="Fail",COUNTIF($E$5:E48,"Fail"),"")</f>
         <v/>
       </c>
@@ -2973,7 +2973,7 @@
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="n"/>
-      <c r="K49">
+      <c r="K49" t="str">
         <f>IF(E49="Fail",COUNTIF($E$5:E49,"Fail"),"")</f>
         <v/>
       </c>
@@ -3008,7 +3008,7 @@
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="n"/>
-      <c r="K50">
+      <c r="K50" t="str">
         <f>IF(E50="Fail",COUNTIF($E$5:E50,"Fail"),"")</f>
         <v/>
       </c>
@@ -3043,7 +3043,7 @@
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="n"/>
-      <c r="K51">
+      <c r="K51" t="str">
         <f>IF(E51="Fail",COUNTIF($E$5:E51,"Fail"),"")</f>
         <v/>
       </c>
@@ -3078,7 +3078,7 @@
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
-      <c r="K52">
+      <c r="K52" t="str">
         <f>IF(E52="Fail",COUNTIF($E$5:E52,"Fail"),"")</f>
         <v/>
       </c>
@@ -3113,7 +3113,7 @@
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
-      <c r="K53">
+      <c r="K53" t="str">
         <f>IF(E53="Fail",COUNTIF($E$5:E53,"Fail"),"")</f>
         <v/>
       </c>
@@ -3148,7 +3148,7 @@
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n"/>
-      <c r="K54">
+      <c r="K54" t="str">
         <f>IF(E54="Fail",COUNTIF($E$5:E54,"Fail"),"")</f>
         <v/>
       </c>
@@ -3183,7 +3183,7 @@
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
-      <c r="K55">
+      <c r="K55" t="str">
         <f>IF(E55="Fail",COUNTIF($E$5:E55,"Fail"),"")</f>
         <v/>
       </c>
@@ -3218,7 +3218,7 @@
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="4" t="n"/>
-      <c r="K56">
+      <c r="K56" t="str">
         <f>IF(E56="Fail",COUNTIF($E$5:E56,"Fail"),"")</f>
         <v/>
       </c>
@@ -3234,7 +3234,7 @@
           <t>6. Access Control</t>
         </is>
       </c>
-      <c r="K57">
+      <c r="K57" t="str">
         <f>IF(E57="Fail",COUNTIF($E$5:E57,"Fail"),"")</f>
         <v/>
       </c>
@@ -3264,7 +3264,7 @@
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
       <c r="H58" s="4" t="n"/>
-      <c r="K58">
+      <c r="K58" t="str">
         <f>IF(E58="Fail",COUNTIF($E$5:E58,"Fail"),"")</f>
         <v/>
       </c>
@@ -3299,7 +3299,7 @@
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
-      <c r="K59">
+      <c r="K59" t="str">
         <f>IF(E59="Fail",COUNTIF($E$5:E59,"Fail"),"")</f>
         <v/>
       </c>
@@ -3334,7 +3334,7 @@
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
-      <c r="K60">
+      <c r="K60" t="str">
         <f>IF(E60="Fail",COUNTIF($E$5:E60,"Fail"),"")</f>
         <v/>
       </c>
@@ -3369,7 +3369,7 @@
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="n"/>
-      <c r="K61">
+      <c r="K61" t="str">
         <f>IF(E61="Fail",COUNTIF($E$5:E61,"Fail"),"")</f>
         <v/>
       </c>
@@ -3404,7 +3404,7 @@
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="4" t="n"/>
-      <c r="K62">
+      <c r="K62" t="str">
         <f>IF(E62="Fail",COUNTIF($E$5:E62,"Fail"),"")</f>
         <v/>
       </c>
@@ -3439,7 +3439,7 @@
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
-      <c r="K63">
+      <c r="K63" t="str">
         <f>IF(E63="Fail",COUNTIF($E$5:E63,"Fail"),"")</f>
         <v/>
       </c>
@@ -3474,7 +3474,7 @@
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
-      <c r="K64">
+      <c r="K64" t="str">
         <f>IF(E64="Fail",COUNTIF($E$5:E64,"Fail"),"")</f>
         <v/>
       </c>
@@ -3509,7 +3509,7 @@
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
-      <c r="K65">
+      <c r="K65" t="str">
         <f>IF(E65="Fail",COUNTIF($E$5:E65,"Fail"),"")</f>
         <v/>
       </c>
@@ -3525,7 +3525,7 @@
           <t>7. Logging, Monitoring &amp; Incident Response</t>
         </is>
       </c>
-      <c r="K66">
+      <c r="K66" t="str">
         <f>IF(E66="Fail",COUNTIF($E$5:E66,"Fail"),"")</f>
         <v/>
       </c>
@@ -3555,7 +3555,7 @@
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="4" t="n"/>
-      <c r="K67">
+      <c r="K67" t="str">
         <f>IF(E67="Fail",COUNTIF($E$5:E67,"Fail"),"")</f>
         <v/>
       </c>
@@ -3590,7 +3590,7 @@
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
-      <c r="K68">
+      <c r="K68" t="str">
         <f>IF(E68="Fail",COUNTIF($E$5:E68,"Fail"),"")</f>
         <v/>
       </c>
@@ -3625,7 +3625,7 @@
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
-      <c r="K69">
+      <c r="K69" t="str">
         <f>IF(E69="Fail",COUNTIF($E$5:E69,"Fail"),"")</f>
         <v/>
       </c>
@@ -3660,7 +3660,7 @@
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
       <c r="H70" s="4" t="n"/>
-      <c r="K70">
+      <c r="K70" t="str">
         <f>IF(E70="Fail",COUNTIF($E$5:E70,"Fail"),"")</f>
         <v/>
       </c>
@@ -3695,7 +3695,7 @@
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="4" t="n"/>
-      <c r="K71">
+      <c r="K71" t="str">
         <f>IF(E71="Fail",COUNTIF($E$5:E71,"Fail"),"")</f>
         <v/>
       </c>
@@ -3730,7 +3730,7 @@
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n"/>
-      <c r="K72">
+      <c r="K72" t="str">
         <f>IF(E72="Fail",COUNTIF($E$5:E72,"Fail"),"")</f>
         <v/>
       </c>
@@ -3765,7 +3765,7 @@
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
-      <c r="K73">
+      <c r="K73" t="str">
         <f>IF(E73="Fail",COUNTIF($E$5:E73,"Fail"),"")</f>
         <v/>
       </c>
@@ -3800,7 +3800,7 @@
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
-      <c r="K74">
+      <c r="K74" t="str">
         <f>IF(E74="Fail",COUNTIF($E$5:E74,"Fail"),"")</f>
         <v/>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="4" t="n"/>
-      <c r="K75">
+      <c r="K75" t="str">
         <f>IF(E75="Fail",COUNTIF($E$5:E75,"Fail"),"")</f>
         <v/>
       </c>
@@ -3870,7 +3870,7 @@
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="n"/>
-      <c r="K76">
+      <c r="K76" t="str">
         <f>IF(E76="Fail",COUNTIF($E$5:E76,"Fail"),"")</f>
         <v/>
       </c>
@@ -3905,7 +3905,7 @@
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
       <c r="H77" s="4" t="n"/>
-      <c r="K77">
+      <c r="K77" t="str">
         <f>IF(E77="Fail",COUNTIF($E$5:E77,"Fail"),"")</f>
         <v/>
       </c>
@@ -3940,7 +3940,7 @@
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
       <c r="H78" s="4" t="n"/>
-      <c r="K78">
+      <c r="K78" t="str">
         <f>IF(E78="Fail",COUNTIF($E$5:E78,"Fail"),"")</f>
         <v/>
       </c>
@@ -3975,7 +3975,7 @@
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="4" t="n"/>
-      <c r="K79">
+      <c r="K79" t="str">
         <f>IF(E79="Fail",COUNTIF($E$5:E79,"Fail"),"")</f>
         <v/>
       </c>
@@ -4010,7 +4010,7 @@
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>
-      <c r="K80">
+      <c r="K80" t="str">
         <f>IF(E80="Fail",COUNTIF($E$5:E80,"Fail"),"")</f>
         <v/>
       </c>
@@ -4045,7 +4045,7 @@
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
-      <c r="K81">
+      <c r="K81" t="str">
         <f>IF(E81="Fail",COUNTIF($E$5:E81,"Fail"),"")</f>
         <v/>
       </c>
@@ -4061,7 +4061,7 @@
           <t>8. Supply Chain Security</t>
         </is>
       </c>
-      <c r="K82">
+      <c r="K82" t="str">
         <f>IF(E82="Fail",COUNTIF($E$5:E82,"Fail"),"")</f>
         <v/>
       </c>
@@ -4091,7 +4091,7 @@
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="4" t="n"/>
-      <c r="K83">
+      <c r="K83" t="str">
         <f>IF(E83="Fail",COUNTIF($E$5:E83,"Fail"),"")</f>
         <v/>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="F84" s="4" t="n"/>
       <c r="G84" s="4" t="n"/>
       <c r="H84" s="4" t="n"/>
-      <c r="K84">
+      <c r="K84" t="str">
         <f>IF(E84="Fail",COUNTIF($E$5:E84,"Fail"),"")</f>
         <v/>
       </c>
@@ -4161,7 +4161,7 @@
       <c r="F85" s="4" t="n"/>
       <c r="G85" s="4" t="n"/>
       <c r="H85" s="4" t="n"/>
-      <c r="K85">
+      <c r="K85" t="str">
         <f>IF(E85="Fail",COUNTIF($E$5:E85,"Fail"),"")</f>
         <v/>
       </c>
@@ -4196,7 +4196,7 @@
       <c r="F86" s="4" t="n"/>
       <c r="G86" s="4" t="n"/>
       <c r="H86" s="4" t="n"/>
-      <c r="K86">
+      <c r="K86" t="str">
         <f>IF(E86="Fail",COUNTIF($E$5:E86,"Fail"),"")</f>
         <v/>
       </c>
@@ -4231,7 +4231,7 @@
       <c r="F87" s="4" t="n"/>
       <c r="G87" s="4" t="n"/>
       <c r="H87" s="4" t="n"/>
-      <c r="K87">
+      <c r="K87" t="str">
         <f>IF(E87="Fail",COUNTIF($E$5:E87,"Fail"),"")</f>
         <v/>
       </c>
@@ -4266,7 +4266,7 @@
       <c r="F88" s="4" t="n"/>
       <c r="G88" s="4" t="n"/>
       <c r="H88" s="4" t="n"/>
-      <c r="K88">
+      <c r="K88" t="str">
         <f>IF(E88="Fail",COUNTIF($E$5:E88,"Fail"),"")</f>
         <v/>
       </c>
@@ -4282,7 +4282,7 @@
           <t>9. Compliance &amp; Governance</t>
         </is>
       </c>
-      <c r="K89">
+      <c r="K89" t="str">
         <f>IF(E89="Fail",COUNTIF($E$5:E89,"Fail"),"")</f>
         <v/>
       </c>
@@ -4312,7 +4312,7 @@
       <c r="F90" s="4" t="n"/>
       <c r="G90" s="4" t="n"/>
       <c r="H90" s="4" t="n"/>
-      <c r="K90">
+      <c r="K90" t="str">
         <f>IF(E90="Fail",COUNTIF($E$5:E90,"Fail"),"")</f>
         <v/>
       </c>
@@ -4347,7 +4347,7 @@
       <c r="F91" s="4" t="n"/>
       <c r="G91" s="4" t="n"/>
       <c r="H91" s="4" t="n"/>
-      <c r="K91">
+      <c r="K91" t="str">
         <f>IF(E91="Fail",COUNTIF($E$5:E91,"Fail"),"")</f>
         <v/>
       </c>
@@ -4382,7 +4382,7 @@
       <c r="F92" s="4" t="n"/>
       <c r="G92" s="4" t="n"/>
       <c r="H92" s="4" t="n"/>
-      <c r="K92">
+      <c r="K92" t="str">
         <f>IF(E92="Fail",COUNTIF($E$5:E92,"Fail"),"")</f>
         <v/>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="F93" s="4" t="n"/>
       <c r="G93" s="4" t="n"/>
       <c r="H93" s="4" t="n"/>
-      <c r="K93">
+      <c r="K93" t="str">
         <f>IF(E93="Fail",COUNTIF($E$5:E93,"Fail"),"")</f>
         <v/>
       </c>
@@ -4452,7 +4452,7 @@
       <c r="F94" s="4" t="n"/>
       <c r="G94" s="4" t="n"/>
       <c r="H94" s="4" t="n"/>
-      <c r="K94">
+      <c r="K94" t="str">
         <f>IF(E94="Fail",COUNTIF($E$5:E94,"Fail"),"")</f>
         <v/>
       </c>
@@ -4487,7 +4487,7 @@
       <c r="F95" s="4" t="n"/>
       <c r="G95" s="4" t="n"/>
       <c r="H95" s="4" t="n"/>
-      <c r="K95">
+      <c r="K95" t="str">
         <f>IF(E95="Fail",COUNTIF($E$5:E95,"Fail"),"")</f>
         <v/>
       </c>
@@ -4503,7 +4503,7 @@
           <t>10. AI Agent Security (ISACA 2026)</t>
         </is>
       </c>
-      <c r="K96">
+      <c r="K96" t="str">
         <f>IF(E96="Fail",COUNTIF($E$5:E96,"Fail"),"")</f>
         <v/>
       </c>
@@ -4533,7 +4533,7 @@
       <c r="F97" s="4" t="n"/>
       <c r="G97" s="4" t="n"/>
       <c r="H97" s="4" t="n"/>
-      <c r="K97">
+      <c r="K97" t="str">
         <f>IF(E97="Fail",COUNTIF($E$5:E97,"Fail"),"")</f>
         <v/>
       </c>
@@ -4568,7 +4568,7 @@
       <c r="F98" s="4" t="n"/>
       <c r="G98" s="4" t="n"/>
       <c r="H98" s="4" t="n"/>
-      <c r="K98">
+      <c r="K98" t="str">
         <f>IF(E98="Fail",COUNTIF($E$5:E98,"Fail"),"")</f>
         <v/>
       </c>
@@ -4603,7 +4603,7 @@
       <c r="F99" s="4" t="n"/>
       <c r="G99" s="4" t="n"/>
       <c r="H99" s="4" t="n"/>
-      <c r="K99">
+      <c r="K99" t="str">
         <f>IF(E99="Fail",COUNTIF($E$5:E99,"Fail"),"")</f>
         <v/>
       </c>
@@ -4638,7 +4638,7 @@
       <c r="F100" s="4" t="n"/>
       <c r="G100" s="4" t="n"/>
       <c r="H100" s="4" t="n"/>
-      <c r="K100">
+      <c r="K100" t="str">
         <f>IF(E100="Fail",COUNTIF($E$5:E100,"Fail"),"")</f>
         <v/>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="F101" s="4" t="n"/>
       <c r="G101" s="4" t="n"/>
       <c r="H101" s="4" t="n"/>
-      <c r="K101">
+      <c r="K101" t="str">
         <f>IF(E101="Fail",COUNTIF($E$5:E101,"Fail"),"")</f>
         <v/>
       </c>
@@ -4708,7 +4708,7 @@
       <c r="F102" s="4" t="n"/>
       <c r="G102" s="4" t="n"/>
       <c r="H102" s="4" t="n"/>
-      <c r="K102">
+      <c r="K102" t="str">
         <f>IF(E102="Fail",COUNTIF($E$5:E102,"Fail"),"")</f>
         <v/>
       </c>
@@ -4743,7 +4743,7 @@
       <c r="F103" s="4" t="n"/>
       <c r="G103" s="4" t="n"/>
       <c r="H103" s="4" t="n"/>
-      <c r="K103">
+      <c r="K103" t="str">
         <f>IF(E103="Fail",COUNTIF($E$5:E103,"Fail"),"")</f>
         <v/>
       </c>
@@ -4778,7 +4778,7 @@
       <c r="F104" s="4" t="n"/>
       <c r="G104" s="4" t="n"/>
       <c r="H104" s="4" t="n"/>
-      <c r="K104">
+      <c r="K104" t="str">
         <f>IF(E104="Fail",COUNTIF($E$5:E104,"Fail"),"")</f>
         <v/>
       </c>
@@ -4813,7 +4813,7 @@
       <c r="F105" s="4" t="n"/>
       <c r="G105" s="4" t="n"/>
       <c r="H105" s="4" t="n"/>
-      <c r="K105">
+      <c r="K105" t="str">
         <f>IF(E105="Fail",COUNTIF($E$5:E105,"Fail"),"")</f>
         <v/>
       </c>
@@ -4848,7 +4848,7 @@
       <c r="F106" s="4" t="n"/>
       <c r="G106" s="4" t="n"/>
       <c r="H106" s="4" t="n"/>
-      <c r="K106">
+      <c r="K106" t="str">
         <f>IF(E106="Fail",COUNTIF($E$5:E106,"Fail"),"")</f>
         <v/>
       </c>
@@ -4883,7 +4883,7 @@
       <c r="F107" s="4" t="n"/>
       <c r="G107" s="4" t="n"/>
       <c r="H107" s="4" t="n"/>
-      <c r="K107">
+      <c r="K107" t="str">
         <f>IF(E107="Fail",COUNTIF($E$5:E107,"Fail"),"")</f>
         <v/>
       </c>
@@ -4918,7 +4918,7 @@
       <c r="F108" s="4" t="n"/>
       <c r="G108" s="4" t="n"/>
       <c r="H108" s="4" t="n"/>
-      <c r="K108">
+      <c r="K108" t="str">
         <f>IF(E108="Fail",COUNTIF($E$5:E108,"Fail"),"")</f>
         <v/>
       </c>
@@ -4953,7 +4953,7 @@
       <c r="F109" s="4" t="n"/>
       <c r="G109" s="4" t="n"/>
       <c r="H109" s="4" t="n"/>
-      <c r="K109">
+      <c r="K109" t="str">
         <f>IF(E109="Fail",COUNTIF($E$5:E109,"Fail"),"")</f>
         <v/>
       </c>
@@ -4988,7 +4988,7 @@
       <c r="F110" s="4" t="n"/>
       <c r="G110" s="4" t="n"/>
       <c r="H110" s="4" t="n"/>
-      <c r="K110">
+      <c r="K110" t="str">
         <f>IF(E110="Fail",COUNTIF($E$5:E110,"Fail"),"")</f>
         <v/>
       </c>
@@ -5023,7 +5023,7 @@
       <c r="F111" s="4" t="n"/>
       <c r="G111" s="4" t="n"/>
       <c r="H111" s="4" t="n"/>
-      <c r="K111">
+      <c r="K111" t="str">
         <f>IF(E111="Fail",COUNTIF($E$5:E111,"Fail"),"")</f>
         <v/>
       </c>
@@ -5058,7 +5058,7 @@
       <c r="F112" s="4" t="n"/>
       <c r="G112" s="4" t="n"/>
       <c r="H112" s="4" t="n"/>
-      <c r="K112">
+      <c r="K112" t="str">
         <f>IF(E112="Fail",COUNTIF($E$5:E112,"Fail"),"")</f>
         <v/>
       </c>
@@ -5093,7 +5093,7 @@
       <c r="F113" s="4" t="n"/>
       <c r="G113" s="4" t="n"/>
       <c r="H113" s="4" t="n"/>
-      <c r="K113">
+      <c r="K113" t="str">
         <f>IF(E113="Fail",COUNTIF($E$5:E113,"Fail"),"")</f>
         <v/>
       </c>
@@ -5128,7 +5128,7 @@
       <c r="F114" s="4" t="n"/>
       <c r="G114" s="4" t="n"/>
       <c r="H114" s="4" t="n"/>
-      <c r="K114">
+      <c r="K114" t="str">
         <f>IF(E114="Fail",COUNTIF($E$5:E114,"Fail"),"")</f>
         <v/>
       </c>
@@ -5163,7 +5163,7 @@
       <c r="F115" s="4" t="n"/>
       <c r="G115" s="4" t="n"/>
       <c r="H115" s="4" t="n"/>
-      <c r="K115">
+      <c r="K115" t="str">
         <f>IF(E115="Fail",COUNTIF($E$5:E115,"Fail"),"")</f>
         <v/>
       </c>
@@ -5198,7 +5198,7 @@
       <c r="F116" s="4" t="n"/>
       <c r="G116" s="4" t="n"/>
       <c r="H116" s="4" t="n"/>
-      <c r="K116">
+      <c r="K116" t="str">
         <f>IF(E116="Fail",COUNTIF($E$5:E116,"Fail"),"")</f>
         <v/>
       </c>
@@ -5233,7 +5233,7 @@
       <c r="F117" s="4" t="n"/>
       <c r="G117" s="4" t="n"/>
       <c r="H117" s="4" t="n"/>
-      <c r="K117">
+      <c r="K117" t="str">
         <f>IF(E117="Fail",COUNTIF($E$5:E117,"Fail"),"")</f>
         <v/>
       </c>
@@ -5268,7 +5268,7 @@
       <c r="F118" s="4" t="n"/>
       <c r="G118" s="4" t="n"/>
       <c r="H118" s="4" t="n"/>
-      <c r="K118">
+      <c r="K118" t="str">
         <f>IF(E118="Fail",COUNTIF($E$5:E118,"Fail"),"")</f>
         <v/>
       </c>
@@ -5303,7 +5303,7 @@
       <c r="F119" s="4" t="n"/>
       <c r="G119" s="4" t="n"/>
       <c r="H119" s="4" t="n"/>
-      <c r="K119">
+      <c r="K119" t="str">
         <f>IF(E119="Fail",COUNTIF($E$5:E119,"Fail"),"")</f>
         <v/>
       </c>
@@ -5319,7 +5319,7 @@
           <t>11. AI Management System (ISO/IEC 42001)</t>
         </is>
       </c>
-      <c r="K120">
+      <c r="K120" t="str">
         <f>IF(E120="Fail",COUNTIF($E$5:E120,"Fail"),"")</f>
         <v/>
       </c>
@@ -5349,7 +5349,7 @@
       <c r="F121" s="4" t="n"/>
       <c r="G121" s="4" t="n"/>
       <c r="H121" s="4" t="n"/>
-      <c r="K121">
+      <c r="K121" t="str">
         <f>IF(E121="Fail",COUNTIF($E$5:E121,"Fail"),"")</f>
         <v/>
       </c>
@@ -5384,7 +5384,7 @@
       <c r="F122" s="4" t="n"/>
       <c r="G122" s="4" t="n"/>
       <c r="H122" s="4" t="n"/>
-      <c r="K122">
+      <c r="K122" t="str">
         <f>IF(E122="Fail",COUNTIF($E$5:E122,"Fail"),"")</f>
         <v/>
       </c>
@@ -5419,7 +5419,7 @@
       <c r="F123" s="4" t="n"/>
       <c r="G123" s="4" t="n"/>
       <c r="H123" s="4" t="n"/>
-      <c r="K123">
+      <c r="K123" t="str">
         <f>IF(E123="Fail",COUNTIF($E$5:E123,"Fail"),"")</f>
         <v/>
       </c>
@@ -5454,7 +5454,7 @@
       <c r="F124" s="4" t="n"/>
       <c r="G124" s="4" t="n"/>
       <c r="H124" s="4" t="n"/>
-      <c r="K124">
+      <c r="K124" t="str">
         <f>IF(E124="Fail",COUNTIF($E$5:E124,"Fail"),"")</f>
         <v/>
       </c>
@@ -5489,7 +5489,7 @@
       <c r="F125" s="4" t="n"/>
       <c r="G125" s="4" t="n"/>
       <c r="H125" s="4" t="n"/>
-      <c r="K125">
+      <c r="K125" t="str">
         <f>IF(E125="Fail",COUNTIF($E$5:E125,"Fail"),"")</f>
         <v/>
       </c>
@@ -5524,7 +5524,7 @@
       <c r="F126" s="4" t="n"/>
       <c r="G126" s="4" t="n"/>
       <c r="H126" s="4" t="n"/>
-      <c r="K126">
+      <c r="K126" t="str">
         <f>IF(E126="Fail",COUNTIF($E$5:E126,"Fail"),"")</f>
         <v/>
       </c>
@@ -5559,7 +5559,7 @@
       <c r="F127" s="4" t="n"/>
       <c r="G127" s="4" t="n"/>
       <c r="H127" s="4" t="n"/>
-      <c r="K127">
+      <c r="K127" t="str">
         <f>IF(E127="Fail",COUNTIF($E$5:E127,"Fail"),"")</f>
         <v/>
       </c>
@@ -5594,7 +5594,7 @@
       <c r="F128" s="4" t="n"/>
       <c r="G128" s="4" t="n"/>
       <c r="H128" s="4" t="n"/>
-      <c r="K128">
+      <c r="K128" t="str">
         <f>IF(E128="Fail",COUNTIF($E$5:E128,"Fail"),"")</f>
         <v/>
       </c>
@@ -5629,7 +5629,7 @@
       <c r="F129" s="4" t="n"/>
       <c r="G129" s="4" t="n"/>
       <c r="H129" s="4" t="n"/>
-      <c r="K129">
+      <c r="K129" t="str">
         <f>IF(E129="Fail",COUNTIF($E$5:E129,"Fail"),"")</f>
         <v/>
       </c>
@@ -5664,7 +5664,7 @@
       <c r="F130" s="4" t="n"/>
       <c r="G130" s="4" t="n"/>
       <c r="H130" s="4" t="n"/>
-      <c r="K130">
+      <c r="K130" t="str">
         <f>IF(E130="Fail",COUNTIF($E$5:E130,"Fail"),"")</f>
         <v/>
       </c>
@@ -5699,7 +5699,7 @@
       <c r="F131" s="4" t="n"/>
       <c r="G131" s="4" t="n"/>
       <c r="H131" s="4" t="n"/>
-      <c r="K131">
+      <c r="K131" t="str">
         <f>IF(E131="Fail",COUNTIF($E$5:E131,"Fail"),"")</f>
         <v/>
       </c>
@@ -5734,7 +5734,7 @@
       <c r="F132" s="4" t="n"/>
       <c r="G132" s="4" t="n"/>
       <c r="H132" s="4" t="n"/>
-      <c r="K132">
+      <c r="K132" t="str">
         <f>IF(E132="Fail",COUNTIF($E$5:E132,"Fail"),"")</f>
         <v/>
       </c>
@@ -5769,7 +5769,7 @@
       <c r="F133" s="4" t="n"/>
       <c r="G133" s="4" t="n"/>
       <c r="H133" s="4" t="n"/>
-      <c r="K133">
+      <c r="K133" t="str">
         <f>IF(E133="Fail",COUNTIF($E$5:E133,"Fail"),"")</f>
         <v/>
       </c>
@@ -5804,7 +5804,7 @@
       <c r="F134" s="4" t="n"/>
       <c r="G134" s="4" t="n"/>
       <c r="H134" s="4" t="n"/>
-      <c r="K134">
+      <c r="K134" t="str">
         <f>IF(E134="Fail",COUNTIF($E$5:E134,"Fail"),"")</f>
         <v/>
       </c>
@@ -5839,7 +5839,7 @@
       <c r="F135" s="4" t="n"/>
       <c r="G135" s="4" t="n"/>
       <c r="H135" s="4" t="n"/>
-      <c r="K135">
+      <c r="K135" t="str">
         <f>IF(E135="Fail",COUNTIF($E$5:E135,"Fail"),"")</f>
         <v/>
       </c>
@@ -5874,7 +5874,7 @@
       <c r="F136" s="4" t="n"/>
       <c r="G136" s="4" t="n"/>
       <c r="H136" s="4" t="n"/>
-      <c r="K136">
+      <c r="K136" t="str">
         <f>IF(E136="Fail",COUNTIF($E$5:E136,"Fail"),"")</f>
         <v/>
       </c>
@@ -5909,7 +5909,7 @@
       <c r="F137" s="4" t="n"/>
       <c r="G137" s="4" t="n"/>
       <c r="H137" s="4" t="n"/>
-      <c r="K137">
+      <c r="K137" t="str">
         <f>IF(E137="Fail",COUNTIF($E$5:E137,"Fail"),"")</f>
         <v/>
       </c>
@@ -6057,23 +6057,23 @@
       <c r="A4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(1,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(1,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(1,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(1,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(1,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6086,23 +6086,23 @@
       <c r="A5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(2,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(2,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(2,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(2,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(2,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6115,23 +6115,23 @@
       <c r="A6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(3,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(3,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(3,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(3,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(3,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6144,23 +6144,23 @@
       <c r="A7" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(4,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(4,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(4,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(4,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(4,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6173,23 +6173,23 @@
       <c r="A8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(5,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(5,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(5,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(5,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(5,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6202,23 +6202,23 @@
       <c r="A9" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(6,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(6,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(6,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(6,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(6,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6231,23 +6231,23 @@
       <c r="A10" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(7,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(7,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(7,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(7,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(7,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6260,23 +6260,23 @@
       <c r="A11" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(8,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(8,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(8,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(8,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(8,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6289,23 +6289,23 @@
       <c r="A12" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(9,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(9,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(9,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(9,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(9,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6318,23 +6318,23 @@
       <c r="A13" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(10,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(10,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(10,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(10,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(10,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6347,23 +6347,23 @@
       <c r="A14" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(11,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(11,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(11,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(11,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(11,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6376,23 +6376,23 @@
       <c r="A15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(12,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(12,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(12,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(12,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(12,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6405,23 +6405,23 @@
       <c r="A16" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(13,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(13,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(13,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(13,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(13,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6434,23 +6434,23 @@
       <c r="A17" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(14,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(14,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(14,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(14,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(14,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6463,23 +6463,23 @@
       <c r="A18" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(15,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(15,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(15,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(15,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(15,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6492,23 +6492,23 @@
       <c r="A19" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(16,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(16,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(16,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(16,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(16,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6521,23 +6521,23 @@
       <c r="A20" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(17,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(17,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(17,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(17,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(17,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6550,23 +6550,23 @@
       <c r="A21" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(18,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(18,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(18,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(18,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(18,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6579,23 +6579,23 @@
       <c r="A22" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(19,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(19,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(19,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(19,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(19,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6608,23 +6608,23 @@
       <c r="A23" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(20,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(20,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(20,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(20,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(20,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6637,23 +6637,23 @@
       <c r="A24" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(21,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(21,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(21,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(21,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(21,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6666,23 +6666,23 @@
       <c r="A25" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(22,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(22,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(22,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(22,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(22,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6695,23 +6695,23 @@
       <c r="A26" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(23,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(23,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(23,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(23,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(23,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6724,23 +6724,23 @@
       <c r="A27" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(24,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(24,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(24,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(24,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(24,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6753,23 +6753,23 @@
       <c r="A28" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(25,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(25,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(25,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(25,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(25,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6782,23 +6782,23 @@
       <c r="A29" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(26,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(26,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(26,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(26,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(26,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6811,23 +6811,23 @@
       <c r="A30" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(27,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(27,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(27,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(27,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(27,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6840,23 +6840,23 @@
       <c r="A31" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(28,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(28,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(28,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(28,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(28,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6869,23 +6869,23 @@
       <c r="A32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(29,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(29,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(29,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(29,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(29,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6898,23 +6898,23 @@
       <c r="A33" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(30,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(30,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(30,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(30,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(30,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6927,23 +6927,23 @@
       <c r="A34" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(31,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(31,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(31,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(31,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(31,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6956,23 +6956,23 @@
       <c r="A35" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(32,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(32,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(32,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(32,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(32,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -6985,23 +6985,23 @@
       <c r="A36" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(33,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(33,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(33,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(33,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(33,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7014,23 +7014,23 @@
       <c r="A37" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(34,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(34,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(34,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(34,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(34,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7043,23 +7043,23 @@
       <c r="A38" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(35,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="17">
+      <c r="C38" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(35,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(35,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(35,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(35,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7072,23 +7072,23 @@
       <c r="A39" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(36,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(36,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(36,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(36,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(36,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7101,23 +7101,23 @@
       <c r="A40" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(37,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(37,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(37,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(37,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(37,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7130,23 +7130,23 @@
       <c r="A41" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(38,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(38,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(38,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(38,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(38,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7159,23 +7159,23 @@
       <c r="A42" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(39,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(39,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(39,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(39,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(39,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7188,23 +7188,23 @@
       <c r="A43" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(40,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(40,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(40,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(40,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(40,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7217,23 +7217,23 @@
       <c r="A44" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(41,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(41,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(41,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(41,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F44" s="24">
+      <c r="F44" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(41,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7246,23 +7246,23 @@
       <c r="A45" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(42,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(42,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(42,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(42,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(42,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7275,23 +7275,23 @@
       <c r="A46" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(43,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(43,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(43,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(43,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(43,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7304,23 +7304,23 @@
       <c r="A47" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(44,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(44,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(44,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(44,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(44,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7333,23 +7333,23 @@
       <c r="A48" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(45,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(45,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(45,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(45,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(45,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7362,23 +7362,23 @@
       <c r="A49" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(46,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(46,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(46,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(46,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F49" s="24">
+      <c r="F49" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(46,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7391,23 +7391,23 @@
       <c r="A50" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(47,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(47,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(47,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(47,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F50" s="24">
+      <c r="F50" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(47,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7420,23 +7420,23 @@
       <c r="A51" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(48,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(48,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(48,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(48,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F51" s="24">
+      <c r="F51" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(48,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7449,23 +7449,23 @@
       <c r="A52" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(49,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C52" s="17">
+      <c r="C52" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(49,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(49,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(49,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F52" s="24">
+      <c r="F52" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(49,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7478,23 +7478,23 @@
       <c r="A53" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(50,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(50,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(50,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(50,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F53" s="24">
+      <c r="F53" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(50,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7507,23 +7507,23 @@
       <c r="A54" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(51,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C54" s="17">
+      <c r="C54" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(51,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D54" s="10">
+      <c r="D54" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(51,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(51,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F54" s="24">
+      <c r="F54" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(51,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7536,23 +7536,23 @@
       <c r="A55" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(52,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C55" s="17">
+      <c r="C55" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(52,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D55" s="10">
+      <c r="D55" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(52,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(52,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F55" s="24">
+      <c r="F55" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(52,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7565,23 +7565,23 @@
       <c r="A56" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(53,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C56" s="17">
+      <c r="C56" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(53,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(53,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(53,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F56" s="24">
+      <c r="F56" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(53,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7594,23 +7594,23 @@
       <c r="A57" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(54,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C57" s="17">
+      <c r="C57" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(54,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D57" s="10">
+      <c r="D57" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(54,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(54,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F57" s="24">
+      <c r="F57" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(54,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7623,23 +7623,23 @@
       <c r="A58" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(55,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C58" s="17">
+      <c r="C58" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(55,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(55,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E58" s="26">
+      <c r="E58" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(55,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F58" s="24">
+      <c r="F58" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(55,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7652,23 +7652,23 @@
       <c r="A59" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(56,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C59" s="17">
+      <c r="C59" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(56,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D59" s="10">
+      <c r="D59" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(56,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(56,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F59" s="24">
+      <c r="F59" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(56,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7681,23 +7681,23 @@
       <c r="A60" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(57,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C60" s="17">
+      <c r="C60" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(57,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D60" s="10">
+      <c r="D60" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(57,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E60" s="26">
+      <c r="E60" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(57,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F60" s="24">
+      <c r="F60" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(57,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7710,23 +7710,23 @@
       <c r="A61" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(58,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C61" s="17">
+      <c r="C61" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(58,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D61" s="10">
+      <c r="D61" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(58,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E61" s="26">
+      <c r="E61" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(58,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F61" s="24">
+      <c r="F61" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(58,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7739,23 +7739,23 @@
       <c r="A62" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(59,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C62" s="17">
+      <c r="C62" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(59,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D62" s="10">
+      <c r="D62" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(59,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E62" s="26">
+      <c r="E62" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(59,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F62" s="24">
+      <c r="F62" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(59,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7768,23 +7768,23 @@
       <c r="A63" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(60,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C63" s="17">
+      <c r="C63" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(60,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(60,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E63" s="26">
+      <c r="E63" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(60,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F63" s="24">
+      <c r="F63" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(60,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7797,23 +7797,23 @@
       <c r="A64" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(61,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C64" s="17">
+      <c r="C64" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(61,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(61,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E64" s="26">
+      <c r="E64" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(61,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F64" s="24">
+      <c r="F64" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(61,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7826,23 +7826,23 @@
       <c r="A65" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(62,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C65" s="17">
+      <c r="C65" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(62,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(62,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E65" s="26">
+      <c r="E65" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(62,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F65" s="24">
+      <c r="F65" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(62,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7855,23 +7855,23 @@
       <c r="A66" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(63,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C66" s="17">
+      <c r="C66" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(63,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(63,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E66" s="26">
+      <c r="E66" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(63,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F66" s="24">
+      <c r="F66" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(63,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7884,23 +7884,23 @@
       <c r="A67" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(64,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C67" s="17">
+      <c r="C67" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(64,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D67" s="10">
+      <c r="D67" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(64,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E67" s="26">
+      <c r="E67" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(64,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F67" s="24">
+      <c r="F67" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(64,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7913,23 +7913,23 @@
       <c r="A68" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(65,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C68" s="17">
+      <c r="C68" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(65,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D68" s="10">
+      <c r="D68" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(65,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E68" s="26">
+      <c r="E68" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(65,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F68" s="24">
+      <c r="F68" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(65,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7942,23 +7942,23 @@
       <c r="A69" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(66,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C69" s="17">
+      <c r="C69" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(66,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(66,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E69" s="26">
+      <c r="E69" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(66,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F69" s="24">
+      <c r="F69" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(66,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -7971,23 +7971,23 @@
       <c r="A70" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(67,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C70" s="17">
+      <c r="C70" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(67,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(67,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E70" s="26">
+      <c r="E70" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(67,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F70" s="24">
+      <c r="F70" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(67,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8000,23 +8000,23 @@
       <c r="A71" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(68,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C71" s="17">
+      <c r="C71" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(68,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(68,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E71" s="26">
+      <c r="E71" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(68,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F71" s="24">
+      <c r="F71" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(68,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8029,23 +8029,23 @@
       <c r="A72" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(69,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C72" s="17">
+      <c r="C72" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(69,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D72" s="10">
+      <c r="D72" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(69,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E72" s="26">
+      <c r="E72" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(69,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F72" s="24">
+      <c r="F72" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(69,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8058,23 +8058,23 @@
       <c r="A73" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(70,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C73" s="17">
+      <c r="C73" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(70,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(70,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E73" s="26">
+      <c r="E73" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(70,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F73" s="24">
+      <c r="F73" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(70,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8087,23 +8087,23 @@
       <c r="A74" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(71,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C74" s="17">
+      <c r="C74" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(71,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D74" s="10">
+      <c r="D74" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(71,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E74" s="26">
+      <c r="E74" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(71,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F74" s="24">
+      <c r="F74" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(71,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8116,23 +8116,23 @@
       <c r="A75" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(72,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C75" s="17">
+      <c r="C75" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(72,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D75" s="10">
+      <c r="D75" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(72,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(72,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F75" s="24">
+      <c r="F75" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(72,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8145,23 +8145,23 @@
       <c r="A76" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(73,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C76" s="17">
+      <c r="C76" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(73,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D76" s="10">
+      <c r="D76" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(73,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E76" s="26">
+      <c r="E76" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(73,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F76" s="24">
+      <c r="F76" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(73,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8174,23 +8174,23 @@
       <c r="A77" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(74,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C77" s="17">
+      <c r="C77" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(74,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D77" s="10">
+      <c r="D77" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(74,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E77" s="26">
+      <c r="E77" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(74,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F77" s="24">
+      <c r="F77" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(74,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8203,23 +8203,23 @@
       <c r="A78" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(75,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C78" s="17">
+      <c r="C78" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(75,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D78" s="10">
+      <c r="D78" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(75,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E78" s="26">
+      <c r="E78" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(75,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F78" s="24">
+      <c r="F78" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(75,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8232,23 +8232,23 @@
       <c r="A79" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(76,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C79" s="17">
+      <c r="C79" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(76,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D79" s="10">
+      <c r="D79" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(76,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E79" s="26">
+      <c r="E79" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(76,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F79" s="24">
+      <c r="F79" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(76,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8261,23 +8261,23 @@
       <c r="A80" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(77,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C80" s="17">
+      <c r="C80" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(77,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D80" s="10">
+      <c r="D80" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(77,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E80" s="26">
+      <c r="E80" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(77,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F80" s="24">
+      <c r="F80" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(77,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8290,23 +8290,23 @@
       <c r="A81" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(78,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C81" s="17">
+      <c r="C81" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(78,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D81" s="10">
+      <c r="D81" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(78,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E81" s="26">
+      <c r="E81" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(78,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F81" s="24">
+      <c r="F81" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(78,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8319,23 +8319,23 @@
       <c r="A82" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(79,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C82" s="17">
+      <c r="C82" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(79,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D82" s="10">
+      <c r="D82" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(79,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E82" s="26">
+      <c r="E82" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(79,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F82" s="24">
+      <c r="F82" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(79,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8348,23 +8348,23 @@
       <c r="A83" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(80,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C83" s="17">
+      <c r="C83" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(80,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D83" s="10">
+      <c r="D83" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(80,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E83" s="26">
+      <c r="E83" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(80,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F83" s="24">
+      <c r="F83" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(80,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8377,23 +8377,23 @@
       <c r="A84" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(81,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C84" s="17">
+      <c r="C84" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(81,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D84" s="10">
+      <c r="D84" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(81,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E84" s="26">
+      <c r="E84" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(81,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F84" s="24">
+      <c r="F84" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(81,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8406,23 +8406,23 @@
       <c r="A85" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(82,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C85" s="17">
+      <c r="C85" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(82,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D85" s="10">
+      <c r="D85" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(82,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E85" s="26">
+      <c r="E85" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(82,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F85" s="24">
+      <c r="F85" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(82,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8435,23 +8435,23 @@
       <c r="A86" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(83,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C86" s="17">
+      <c r="C86" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(83,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D86" s="10">
+      <c r="D86" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(83,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E86" s="26">
+      <c r="E86" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(83,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F86" s="24">
+      <c r="F86" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(83,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8464,23 +8464,23 @@
       <c r="A87" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(84,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C87" s="17">
+      <c r="C87" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(84,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D87" s="10">
+      <c r="D87" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(84,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E87" s="26">
+      <c r="E87" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(84,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F87" s="24">
+      <c r="F87" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(84,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8493,23 +8493,23 @@
       <c r="A88" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(85,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C88" s="17">
+      <c r="C88" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(85,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D88" s="10">
+      <c r="D88" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(85,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E88" s="26">
+      <c r="E88" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(85,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F88" s="24">
+      <c r="F88" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(85,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8522,23 +8522,23 @@
       <c r="A89" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(86,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C89" s="17">
+      <c r="C89" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(86,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D89" s="10">
+      <c r="D89" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(86,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E89" s="26">
+      <c r="E89" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(86,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F89" s="24">
+      <c r="F89" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(86,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8551,23 +8551,23 @@
       <c r="A90" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(87,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C90" s="17">
+      <c r="C90" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(87,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D90" s="10">
+      <c r="D90" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(87,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E90" s="26">
+      <c r="E90" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(87,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F90" s="24">
+      <c r="F90" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(87,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8580,23 +8580,23 @@
       <c r="A91" s="8" t="n">
         <v>88</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(88,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C91" s="17">
+      <c r="C91" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(88,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D91" s="10">
+      <c r="D91" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(88,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E91" s="26">
+      <c r="E91" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(88,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F91" s="24">
+      <c r="F91" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(88,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8609,23 +8609,23 @@
       <c r="A92" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(89,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C92" s="17">
+      <c r="C92" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(89,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D92" s="10">
+      <c r="D92" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(89,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E92" s="26">
+      <c r="E92" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(89,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F92" s="24">
+      <c r="F92" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(89,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8638,23 +8638,23 @@
       <c r="A93" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(90,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C93" s="17">
+      <c r="C93" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(90,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D93" s="10">
+      <c r="D93" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(90,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E93" s="26">
+      <c r="E93" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(90,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F93" s="24">
+      <c r="F93" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(90,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8667,23 +8667,23 @@
       <c r="A94" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(91,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C94" s="17">
+      <c r="C94" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(91,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D94" s="10">
+      <c r="D94" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(91,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E94" s="26">
+      <c r="E94" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(91,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F94" s="24">
+      <c r="F94" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(91,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8696,23 +8696,23 @@
       <c r="A95" s="8" t="n">
         <v>92</v>
       </c>
-      <c r="B95" s="10">
+      <c r="B95" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(92,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C95" s="17">
+      <c r="C95" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(92,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D95" s="10">
+      <c r="D95" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(92,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E95" s="26">
+      <c r="E95" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(92,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F95" s="24">
+      <c r="F95" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(92,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8725,23 +8725,23 @@
       <c r="A96" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="B96" s="10">
+      <c r="B96" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(93,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C96" s="17">
+      <c r="C96" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(93,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D96" s="10">
+      <c r="D96" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(93,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E96" s="26">
+      <c r="E96" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(93,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F96" s="24">
+      <c r="F96" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(93,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8754,23 +8754,23 @@
       <c r="A97" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="B97" s="10">
+      <c r="B97" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(94,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C97" s="17">
+      <c r="C97" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(94,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D97" s="10">
+      <c r="D97" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(94,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E97" s="26">
+      <c r="E97" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(94,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F97" s="24">
+      <c r="F97" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(94,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8783,23 +8783,23 @@
       <c r="A98" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(95,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C98" s="17">
+      <c r="C98" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(95,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D98" s="10">
+      <c r="D98" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(95,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E98" s="26">
+      <c r="E98" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(95,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F98" s="24">
+      <c r="F98" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(95,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8812,23 +8812,23 @@
       <c r="A99" s="8" t="n">
         <v>96</v>
       </c>
-      <c r="B99" s="10">
+      <c r="B99" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(96,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C99" s="17">
+      <c r="C99" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(96,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D99" s="10">
+      <c r="D99" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(96,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E99" s="26">
+      <c r="E99" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(96,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F99" s="24">
+      <c r="F99" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(96,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8841,23 +8841,23 @@
       <c r="A100" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="B100" s="10">
+      <c r="B100" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(97,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C100" s="17">
+      <c r="C100" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(97,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D100" s="10">
+      <c r="D100" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(97,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E100" s="26">
+      <c r="E100" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(97,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F100" s="24">
+      <c r="F100" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(97,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8870,23 +8870,23 @@
       <c r="A101" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="B101" s="10">
+      <c r="B101" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(98,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C101" s="17">
+      <c r="C101" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(98,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D101" s="10">
+      <c r="D101" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(98,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E101" s="26">
+      <c r="E101" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(98,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F101" s="24">
+      <c r="F101" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(98,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8899,23 +8899,23 @@
       <c r="A102" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B102" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(99,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C102" s="17">
+      <c r="C102" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(99,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D102" s="10">
+      <c r="D102" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(99,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E102" s="26">
+      <c r="E102" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(99,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F102" s="24">
+      <c r="F102" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(99,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8928,23 +8928,23 @@
       <c r="A103" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(100,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C103" s="17">
+      <c r="C103" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(100,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D103" s="10">
+      <c r="D103" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(100,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E103" s="26">
+      <c r="E103" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(100,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F103" s="24">
+      <c r="F103" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(100,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8957,23 +8957,23 @@
       <c r="A104" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="B104" s="10">
+      <c r="B104" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(101,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C104" s="17">
+      <c r="C104" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(101,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D104" s="10">
+      <c r="D104" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(101,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E104" s="26">
+      <c r="E104" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(101,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F104" s="24">
+      <c r="F104" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(101,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -8986,23 +8986,23 @@
       <c r="A105" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="B105" s="10">
+      <c r="B105" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(102,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C105" s="17">
+      <c r="C105" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(102,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D105" s="10">
+      <c r="D105" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(102,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E105" s="26">
+      <c r="E105" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(102,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F105" s="24">
+      <c r="F105" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(102,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9015,23 +9015,23 @@
       <c r="A106" s="8" t="n">
         <v>103</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(103,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C106" s="17">
+      <c r="C106" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(103,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D106" s="10">
+      <c r="D106" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(103,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E106" s="26">
+      <c r="E106" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(103,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F106" s="24">
+      <c r="F106" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(103,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9044,23 +9044,23 @@
       <c r="A107" s="8" t="n">
         <v>104</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(104,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C107" s="17">
+      <c r="C107" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(104,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D107" s="10">
+      <c r="D107" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(104,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E107" s="26">
+      <c r="E107" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(104,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F107" s="24">
+      <c r="F107" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(104,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9073,23 +9073,23 @@
       <c r="A108" s="8" t="n">
         <v>105</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(105,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C108" s="17">
+      <c r="C108" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(105,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D108" s="10">
+      <c r="D108" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(105,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E108" s="26">
+      <c r="E108" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(105,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F108" s="24">
+      <c r="F108" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(105,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9102,23 +9102,23 @@
       <c r="A109" s="8" t="n">
         <v>106</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(106,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C109" s="17">
+      <c r="C109" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(106,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D109" s="10">
+      <c r="D109" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(106,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E109" s="26">
+      <c r="E109" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(106,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F109" s="24">
+      <c r="F109" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(106,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9131,23 +9131,23 @@
       <c r="A110" s="8" t="n">
         <v>107</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(107,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C110" s="17">
+      <c r="C110" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(107,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D110" s="10">
+      <c r="D110" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(107,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E110" s="26">
+      <c r="E110" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(107,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F110" s="24">
+      <c r="F110" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(107,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9160,23 +9160,23 @@
       <c r="A111" s="8" t="n">
         <v>108</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(108,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C111" s="17">
+      <c r="C111" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(108,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D111" s="10">
+      <c r="D111" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(108,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E111" s="26">
+      <c r="E111" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(108,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F111" s="24">
+      <c r="F111" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(108,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9189,23 +9189,23 @@
       <c r="A112" s="8" t="n">
         <v>109</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(109,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C112" s="17">
+      <c r="C112" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(109,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D112" s="10">
+      <c r="D112" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(109,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E112" s="26">
+      <c r="E112" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(109,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F112" s="24">
+      <c r="F112" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(109,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9218,23 +9218,23 @@
       <c r="A113" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(110,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C113" s="17">
+      <c r="C113" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(110,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D113" s="10">
+      <c r="D113" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(110,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E113" s="26">
+      <c r="E113" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(110,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F113" s="24">
+      <c r="F113" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(110,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9247,23 +9247,23 @@
       <c r="A114" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="B114" s="10">
+      <c r="B114" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(111,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C114" s="17">
+      <c r="C114" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(111,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D114" s="10">
+      <c r="D114" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(111,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E114" s="26">
+      <c r="E114" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(111,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F114" s="24">
+      <c r="F114" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(111,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9276,23 +9276,23 @@
       <c r="A115" s="8" t="n">
         <v>112</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(112,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C115" s="17">
+      <c r="C115" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(112,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D115" s="10">
+      <c r="D115" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(112,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E115" s="26">
+      <c r="E115" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(112,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F115" s="24">
+      <c r="F115" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(112,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9305,23 +9305,23 @@
       <c r="A116" s="8" t="n">
         <v>113</v>
       </c>
-      <c r="B116" s="10">
+      <c r="B116" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(113,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C116" s="17">
+      <c r="C116" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(113,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D116" s="10">
+      <c r="D116" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(113,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E116" s="26">
+      <c r="E116" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(113,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F116" s="24">
+      <c r="F116" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(113,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9334,23 +9334,23 @@
       <c r="A117" s="8" t="n">
         <v>114</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(114,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C117" s="17">
+      <c r="C117" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(114,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D117" s="10">
+      <c r="D117" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(114,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E117" s="26">
+      <c r="E117" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(114,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F117" s="24">
+      <c r="F117" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(114,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9363,23 +9363,23 @@
       <c r="A118" s="8" t="n">
         <v>115</v>
       </c>
-      <c r="B118" s="10">
+      <c r="B118" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(115,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C118" s="17">
+      <c r="C118" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(115,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D118" s="10">
+      <c r="D118" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(115,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E118" s="26">
+      <c r="E118" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(115,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F118" s="24">
+      <c r="F118" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(115,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9392,23 +9392,23 @@
       <c r="A119" s="8" t="n">
         <v>116</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B119" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(116,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C119" s="17">
+      <c r="C119" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(116,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D119" s="10">
+      <c r="D119" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(116,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E119" s="26">
+      <c r="E119" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(116,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F119" s="24">
+      <c r="F119" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(116,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9421,23 +9421,23 @@
       <c r="A120" s="8" t="n">
         <v>117</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(117,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C120" s="17">
+      <c r="C120" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(117,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D120" s="10">
+      <c r="D120" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(117,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E120" s="26">
+      <c r="E120" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(117,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F120" s="24">
+      <c r="F120" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(117,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9450,23 +9450,23 @@
       <c r="A121" s="8" t="n">
         <v>118</v>
       </c>
-      <c r="B121" s="10">
+      <c r="B121" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(118,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C121" s="17">
+      <c r="C121" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(118,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D121" s="10">
+      <c r="D121" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(118,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E121" s="26">
+      <c r="E121" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(118,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F121" s="24">
+      <c r="F121" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(118,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9479,23 +9479,23 @@
       <c r="A122" s="8" t="n">
         <v>119</v>
       </c>
-      <c r="B122" s="10">
+      <c r="B122" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(119,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C122" s="17">
+      <c r="C122" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(119,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D122" s="10">
+      <c r="D122" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(119,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E122" s="26">
+      <c r="E122" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(119,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F122" s="24">
+      <c r="F122" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(119,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9508,23 +9508,23 @@
       <c r="A123" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(120,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C123" s="17">
+      <c r="C123" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(120,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D123" s="10">
+      <c r="D123" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(120,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E123" s="26">
+      <c r="E123" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(120,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F123" s="24">
+      <c r="F123" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(120,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9537,23 +9537,23 @@
       <c r="A124" s="8" t="n">
         <v>121</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(121,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C124" s="17">
+      <c r="C124" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(121,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D124" s="10">
+      <c r="D124" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(121,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E124" s="26">
+      <c r="E124" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(121,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F124" s="24">
+      <c r="F124" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(121,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9566,23 +9566,23 @@
       <c r="A125" s="8" t="n">
         <v>122</v>
       </c>
-      <c r="B125" s="10">
+      <c r="B125" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(122,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C125" s="17">
+      <c r="C125" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(122,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D125" s="10">
+      <c r="D125" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(122,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E125" s="26">
+      <c r="E125" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(122,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F125" s="24">
+      <c r="F125" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(122,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9595,23 +9595,23 @@
       <c r="A126" s="8" t="n">
         <v>123</v>
       </c>
-      <c r="B126" s="10">
+      <c r="B126" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(123,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C126" s="17">
+      <c r="C126" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(123,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D126" s="10">
+      <c r="D126" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(123,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E126" s="26">
+      <c r="E126" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(123,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F126" s="24">
+      <c r="F126" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(123,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9624,23 +9624,23 @@
       <c r="A127" s="8" t="n">
         <v>124</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B127" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(124,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C127" s="17">
+      <c r="C127" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(124,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D127" s="10">
+      <c r="D127" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(124,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E127" s="26">
+      <c r="E127" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(124,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F127" s="24">
+      <c r="F127" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(124,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
@@ -9653,23 +9653,23 @@
       <c r="A128" s="8" t="n">
         <v>125</v>
       </c>
-      <c r="B128" s="10">
+      <c r="B128" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$A$5:$A$137,MATCH(125,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="C128" s="17">
+      <c r="C128" s="17" t="str">
         <f>IFERROR(INDEX(Checklist!$B$5:$B$137,MATCH(125,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="D128" s="10">
+      <c r="D128" s="10" t="str">
         <f>IFERROR(INDEX(Checklist!$F$5:$F$137,MATCH(125,Checklist!$K$5:$K$137,0))&amp;"","")</f>
         <v/>
       </c>
-      <c r="E128" s="26">
+      <c r="E128" s="26" t="str">
         <f>IFERROR(INDEX(Checklist!$L$5:$L$137,MATCH(125,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
-      <c r="F128" s="24">
+      <c r="F128" s="24" t="str">
         <f>IFERROR(INDEX(Checklist!$D$5:$D$137,MATCH(125,Checklist!$K$5:$K$137,0)),"")</f>
         <v/>
       </c>
